--- a/analysis/data/annotation/[Archived] Labeling SDG 16_ Peace, justice and strong institutions - Benchmarking Dataset.xlsx
+++ b/analysis/data/annotation/[Archived] Labeling SDG 16_ Peace, justice and strong institutions - Benchmarking Dataset.xlsx
@@ -3359,7 +3359,7 @@
     <row r="2">
       <c r="A2" s="24" t="str">
         <f t="shared" ref="A2:A69" si="1">IF(NOT(ISBLANK(B2)), LEFT(MD5(B2), 7), "")</f>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B2" s="56" t="s">
         <v>258</v>
@@ -3380,7 +3380,7 @@
     <row r="3">
       <c r="A3" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>272</v>
@@ -3401,7 +3401,7 @@
     <row r="4">
       <c r="A4" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B4" s="58" t="s">
         <v>198</v>
@@ -3422,7 +3422,7 @@
     <row r="5">
       <c r="A5" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>223</v>
@@ -3443,7 +3443,7 @@
     <row r="6">
       <c r="A6" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>266</v>
@@ -3464,7 +3464,7 @@
     <row r="7">
       <c r="A7" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>184</v>
@@ -3485,7 +3485,7 @@
     <row r="8">
       <c r="A8" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>306</v>
@@ -3506,7 +3506,7 @@
     <row r="9">
       <c r="A9" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B9" s="58" t="s">
         <v>274</v>
@@ -3527,7 +3527,7 @@
     <row r="10">
       <c r="A10" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>150</v>
@@ -3551,7 +3551,7 @@
     <row r="11">
       <c r="A11" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>146</v>
@@ -3572,7 +3572,7 @@
     <row r="12">
       <c r="A12" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B12" s="58" t="s">
         <v>521</v>
@@ -3596,7 +3596,7 @@
     <row r="13">
       <c r="A13" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>170</v>
@@ -3617,7 +3617,7 @@
     <row r="14">
       <c r="A14" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>284</v>
@@ -3638,7 +3638,7 @@
     <row r="15">
       <c r="A15" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B15" s="58" t="s">
         <v>523</v>
@@ -3662,7 +3662,7 @@
     <row r="16">
       <c r="A16" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B16" s="58" t="s">
         <v>525</v>
@@ -3686,7 +3686,7 @@
     <row r="17">
       <c r="A17" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>260</v>
@@ -3707,7 +3707,7 @@
     <row r="18">
       <c r="A18" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>248</v>
@@ -3728,7 +3728,7 @@
     <row r="19">
       <c r="A19" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>270</v>
@@ -3749,7 +3749,7 @@
     <row r="20">
       <c r="A20" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B20" s="58" t="s">
         <v>304</v>
@@ -3770,7 +3770,7 @@
     <row r="21">
       <c r="A21" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>121</v>
@@ -3794,7 +3794,7 @@
     <row r="22">
       <c r="A22" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>136</v>
@@ -3815,7 +3815,7 @@
     <row r="23">
       <c r="A23" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B23" s="58" t="s">
         <v>194</v>
@@ -3836,7 +3836,7 @@
     <row r="24">
       <c r="A24" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>132</v>
@@ -3857,7 +3857,7 @@
     <row r="25">
       <c r="A25" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>100</v>
@@ -3878,7 +3878,7 @@
     <row r="26">
       <c r="A26" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>164</v>
@@ -3899,7 +3899,7 @@
     <row r="27">
       <c r="A27" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>232</v>
@@ -3920,7 +3920,7 @@
     <row r="28">
       <c r="A28" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>158</v>
@@ -3941,7 +3941,7 @@
     <row r="29">
       <c r="A29" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>300</v>
@@ -3962,7 +3962,7 @@
     <row r="30">
       <c r="A30" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>204</v>
@@ -3983,7 +3983,7 @@
     <row r="31">
       <c r="A31" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B31" s="58" t="s">
         <v>295</v>
@@ -4004,7 +4004,7 @@
     <row r="32">
       <c r="A32" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>156</v>
@@ -4025,7 +4025,7 @@
     <row r="33">
       <c r="A33" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B33" s="58" t="s">
         <v>104</v>
@@ -4049,7 +4049,7 @@
     <row r="34">
       <c r="A34" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>202</v>
@@ -4070,7 +4070,7 @@
     <row r="35">
       <c r="A35" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>239</v>
@@ -4094,7 +4094,7 @@
     <row r="36">
       <c r="A36" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>213</v>
@@ -4115,7 +4115,7 @@
     <row r="37">
       <c r="A37" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B37" s="58" t="s">
         <v>138</v>
@@ -4136,7 +4136,7 @@
     <row r="38">
       <c r="A38" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>256</v>
@@ -4157,7 +4157,7 @@
     <row r="39">
       <c r="A39" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>186</v>
@@ -4178,7 +4178,7 @@
     <row r="40">
       <c r="A40" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>196</v>
@@ -4199,7 +4199,7 @@
     <row r="41">
       <c r="A41" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>234</v>
@@ -4220,7 +4220,7 @@
     <row r="42">
       <c r="A42" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>144</v>
@@ -4241,7 +4241,7 @@
     <row r="43">
       <c r="A43" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>286</v>
@@ -4262,7 +4262,7 @@
     <row r="44">
       <c r="A44" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B44" s="58" t="s">
         <v>176</v>
@@ -4283,7 +4283,7 @@
     <row r="45">
       <c r="A45" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>172</v>
@@ -4304,7 +4304,7 @@
     <row r="46">
       <c r="A46" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>113</v>
@@ -4325,7 +4325,7 @@
     <row r="47">
       <c r="A47" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>102</v>
@@ -4346,7 +4346,7 @@
     <row r="48">
       <c r="A48" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>119</v>
@@ -4367,7 +4367,7 @@
     <row r="49">
       <c r="A49" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>106</v>
@@ -4388,7 +4388,7 @@
     <row r="50">
       <c r="A50" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B50" s="58" t="s">
         <v>153</v>
@@ -4412,7 +4412,7 @@
     <row r="51">
       <c r="A51" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>293</v>
@@ -4433,7 +4433,7 @@
     <row r="52">
       <c r="A52" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>242</v>
@@ -4454,7 +4454,7 @@
     <row r="53">
       <c r="A53" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>160</v>
@@ -4475,7 +4475,7 @@
     <row r="54">
       <c r="A54" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>250</v>
@@ -4496,7 +4496,7 @@
     <row r="55">
       <c r="A55" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B55" s="58" t="s">
         <v>126</v>
@@ -4517,7 +4517,7 @@
     <row r="56">
       <c r="A56" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>168</v>
@@ -4538,7 +4538,7 @@
     <row r="57">
       <c r="A57" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>268</v>
@@ -4559,7 +4559,7 @@
     <row r="58">
       <c r="A58" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B58" s="58" t="s">
         <v>108</v>
@@ -4580,7 +4580,7 @@
     <row r="59">
       <c r="A59" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>182</v>
@@ -4601,7 +4601,7 @@
     <row r="60">
       <c r="A60" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>140</v>
@@ -4622,7 +4622,7 @@
     <row r="61">
       <c r="A61" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B61" s="58" t="s">
         <v>264</v>
@@ -4643,7 +4643,7 @@
     <row r="62">
       <c r="A62" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>180</v>
@@ -4664,7 +4664,7 @@
     <row r="63">
       <c r="A63" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B63" s="12" t="s">
         <v>225</v>
@@ -4685,7 +4685,7 @@
     <row r="64">
       <c r="A64" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>311</v>
@@ -4706,7 +4706,7 @@
     <row r="65">
       <c r="A65" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B65" s="58" t="s">
         <v>526</v>
@@ -4730,7 +4730,7 @@
     <row r="66">
       <c r="A66" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B66" s="58" t="s">
         <v>288</v>
@@ -4751,7 +4751,7 @@
     <row r="67">
       <c r="A67" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>188</v>
@@ -4772,7 +4772,7 @@
     <row r="68">
       <c r="A68" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>302</v>
@@ -4793,7 +4793,7 @@
     <row r="69">
       <c r="A69" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>148</v>
